--- a/outputs/evaluation/architecture/design/v2/CF_M01/run_1/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v2/CF_M01/run_1/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7188</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9817</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.125</v>
       </c>
       <c r="D4" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.9099</v>
       </c>
     </row>
@@ -1226,13 +1240,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -1256,13 +1268,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1308,13 +1318,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>SQL database</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1365,7 +1371,6 @@
       <c r="D4" t="n">
         <v>0.9099</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1386,7 +1391,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_23</t>
@@ -1397,7 +1401,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1416,7 +1419,6 @@
           <t>CF_M01_AU01, CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU24</t>
@@ -1472,13 +1474,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,13 +1552,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1636,13 +1630,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>AWS RDS</t>
@@ -1666,13 +1658,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU35</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1718,13 +1708,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Analytical module</t>
@@ -1748,13 +1736,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU12</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1800,13 +1786,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -1830,13 +1814,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1882,13 +1864,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -1912,13 +1892,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1959,14 +1937,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -1990,13 +1965,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2037,14 +2010,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -2068,13 +2038,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2115,14 +2083,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2146,13 +2111,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2193,14 +2156,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2224,13 +2184,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2276,13 +2234,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -2306,13 +2262,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2358,13 +2312,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2388,13 +2340,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2435,14 +2385,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -2466,13 +2413,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2513,14 +2458,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Business Layer</t>
@@ -2544,13 +2486,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2591,14 +2531,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Server</t>
@@ -2622,13 +2559,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2669,14 +2604,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -2702,13 +2634,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2749,14 +2679,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2775,14 +2702,11 @@
       <c r="P21" t="n">
         <v>41</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2828,13 +2752,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2858,13 +2780,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2905,14 +2825,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -2936,13 +2853,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2983,14 +2898,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Data Layer</t>
@@ -3014,13 +2926,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3061,14 +2971,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3092,13 +2999,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3172,7 +3077,6 @@
           <t>Data Lake</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A centralized repository that allows the storage of structured and unstructured data at any scale.</t>
@@ -3208,7 +3112,6 @@
           <t>Layered Architecture</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
@@ -3300,7 +3203,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
@@ -3336,7 +3238,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -3347,7 +3248,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.8325</v>
       </c>
@@ -3368,7 +3268,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -3379,7 +3278,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.6941000000000001</v>
       </c>
@@ -3400,7 +3298,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -3411,7 +3308,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.7309</v>
       </c>
@@ -3432,7 +3328,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -3463,7 +3358,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -3499,7 +3393,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>presentation layer, api gateway service</t>
@@ -3535,7 +3428,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>api gateway service, core service, analytical module</t>
@@ -3576,7 +3468,6 @@
           <t>TCP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>communication between the Api Gateway service is via the TCP communication protocol</t>
@@ -3607,7 +3498,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>player, api player</t>
@@ -3643,7 +3533,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>player, web socket</t>
@@ -3684,7 +3573,6 @@
           <t>AWS cloud services set</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
@@ -3715,7 +3603,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>analytical module, aws cloud services set, sql database</t>
@@ -3751,7 +3638,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>core service, sql database, aws cloud services set</t>
@@ -3792,7 +3678,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
@@ -3828,7 +3713,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
